--- a/outputs/q3/validation/q3_validation.xlsx
+++ b/outputs/q3/validation/q3_validation.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42100.58456896836</v>
+        <v>41076.42622345466</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>23655.43013907938</v>
+        <v>23544.64892563613</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>18445.15442988898</v>
+        <v>17531.77729781853</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.5618788998126026</v>
+        <v>0.5731912702812525</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.4381211001873973</v>
+        <v>0.4268087297187476</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.2736390075037605</v>
+        <v>1.75998298136706</v>
       </c>
     </row>
     <row r="12">
